--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/6mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/6mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.63620125</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>758.914822170277</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>753.9017619367982</v>
+        <v>0.248963864</v>
+      </c>
+      <c r="Y2">
+        <v>0.262598838</v>
+      </c>
+      <c r="Z2">
+        <v>0.361857921423258</v>
+      </c>
+      <c r="AA2">
+        <v>6.817487</v>
+      </c>
+      <c r="AB2">
+        <v>0.05401170157749619</v>
+      </c>
+      <c r="AC2">
+        <v>40.99028089779959</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.63631699074</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>758.0995859110402</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>755.8534769205453</v>
+      </c>
+      <c r="X3">
+        <v>0.24894385</v>
+      </c>
+      <c r="Y3">
+        <v>0.262589606</v>
+      </c>
+      <c r="Z3">
+        <v>0.3618374519477741</v>
+      </c>
+      <c r="AA3">
+        <v>6.822878000000003</v>
+      </c>
+      <c r="AB3">
+        <v>0.05396754028373912</v>
+      </c>
+      <c r="AC3">
+        <v>40.91276994174001</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.63643273148</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>755.4497757571593</v>
       </c>
-      <c r="V4">
-        <v>1.811659030421436</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.248944486</v>
+      </c>
+      <c r="Y4">
+        <v>0.262587696</v>
+      </c>
+      <c r="Z4">
+        <v>0.3618365034105771</v>
+      </c>
+      <c r="AA4">
+        <v>6.821604999999998</v>
+      </c>
+      <c r="AB4">
+        <v>0.05397712892878643</v>
+      </c>
+      <c r="AC4">
+        <v>40.77700994526698</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.63654905093</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>758.3868111456941</v>
       </c>
-      <c r="V5">
-        <v>1.619164859865443</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>40.86966822010724</v>
+      </c>
+      <c r="X5">
+        <v>0.248920342</v>
+      </c>
+      <c r="Y5">
+        <v>0.262578464</v>
+      </c>
+      <c r="Z5">
+        <v>0.361813192708608</v>
+      </c>
+      <c r="AA5">
+        <v>6.829060999999996</v>
+      </c>
+      <c r="AB5">
+        <v>0.05391686600132364</v>
+      </c>
+      <c r="AC5">
+        <v>40.88984007371352</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.63666537037</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>758.003225198103</v>
       </c>
-      <c r="V6">
-        <v>1.596528478718279</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.24891081</v>
+      </c>
+      <c r="Y6">
+        <v>0.262571142</v>
+      </c>
+      <c r="Z6">
+        <v>0.361801321094935</v>
+      </c>
+      <c r="AA6">
+        <v>6.830165999999998</v>
+      </c>
+      <c r="AB6">
+        <v>0.0539067353408779</v>
+      </c>
+      <c r="AC6">
+        <v>40.86147924828601</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.63678111111</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>757.9769312434786</v>
       </c>
-      <c r="V7">
-        <v>0.2294308485069262</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.248943214</v>
+      </c>
+      <c r="Y7">
+        <v>0.262565094</v>
+      </c>
+      <c r="Z7">
+        <v>0.3618192261114362</v>
+      </c>
+      <c r="AA7">
+        <v>6.810940000000002</v>
+      </c>
+      <c r="AB7">
+        <v>0.0540562580242914</v>
+      </c>
+      <c r="AC7">
+        <v>40.97339657175806</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.63689685185</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>753.9145372576271</v>
       </c>
-      <c r="V8">
-        <v>2.353051399882182</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.248973714</v>
+      </c>
+      <c r="Y8">
+        <v>0.262557134</v>
+      </c>
+      <c r="Z8">
+        <v>0.3618344357261312</v>
+      </c>
+      <c r="AA8">
+        <v>6.791710000000002</v>
+      </c>
+      <c r="AB8">
+        <v>0.0542062828114414</v>
+      </c>
+      <c r="AC8">
+        <v>40.86690462224391</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.63701259259</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>752.8037375874356</v>
       </c>
-      <c r="V9">
-        <v>2.723320687644052</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.248954652</v>
+      </c>
+      <c r="Y9">
+        <v>0.262548222</v>
+      </c>
+      <c r="Z9">
+        <v>0.3618148526909894</v>
+      </c>
+      <c r="AA9">
+        <v>6.796785</v>
+      </c>
+      <c r="AB9">
+        <v>0.0541643545275248</v>
+      </c>
+      <c r="AC9">
+        <v>40.77512853233161</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.63712891204</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>751.474138936796</v>
       </c>
-      <c r="V10">
-        <v>1.221832806578613</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.24893972</v>
+      </c>
+      <c r="Y10">
+        <v>0.262530394</v>
+      </c>
+      <c r="Z10">
+        <v>0.3617916416495461</v>
+      </c>
+      <c r="AA10">
+        <v>6.795337000000004</v>
+      </c>
+      <c r="AB10">
+        <v>0.05417214586236298</v>
+      </c>
+      <c r="AC10">
+        <v>40.70896666627773</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.63724523148</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>754.6685544280778</v>
       </c>
-      <c r="V11">
-        <v>1.604663243584197</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.248932096</v>
+      </c>
+      <c r="Y11">
+        <v>0.262522118</v>
+      </c>
+      <c r="Z11">
+        <v>0.3617803903726115</v>
+      </c>
+      <c r="AA11">
+        <v>6.795011000000002</v>
+      </c>
+      <c r="AB11">
+        <v>0.05417302892488139</v>
+      </c>
+      <c r="AC11">
+        <v>40.88268142773068</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.63736155093</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>755.2942103958941</v>
       </c>
-      <c r="V12">
-        <v>2.048929870022254</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.248924788</v>
+      </c>
+      <c r="Y12">
+        <v>0.262520526</v>
+      </c>
+      <c r="Z12">
+        <v>0.3617742067259102</v>
+      </c>
+      <c r="AA12">
+        <v>6.797868999999999</v>
+      </c>
+      <c r="AB12">
+        <v>0.05415013541982543</v>
+      </c>
+      <c r="AC12">
+        <v>40.89928377474779</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.63747729167</v>
       </c>
@@ -1340,11 +1556,26 @@
       <c r="U13">
         <v>755.2553930149586</v>
       </c>
-      <c r="V13">
-        <v>0.3505547285316822</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.24892606</v>
+      </c>
+      <c r="Y13">
+        <v>0.26252148</v>
+      </c>
+      <c r="Z13">
+        <v>0.3617757742145181</v>
+      </c>
+      <c r="AA13">
+        <v>6.797709999999995</v>
+      </c>
+      <c r="AB13">
+        <v>0.05415158543406916</v>
+      </c>
+      <c r="AC13">
+        <v>40.89827693939101</v>
       </c>
     </row>
   </sheetData>
